--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104528_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104528_W8.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.315</v>
+        <v>5.56</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7286</v>
+        <v>3.629</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5864</v>
+        <v>1.931</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8201</v>
+        <v>3.8015</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.5108</v>
+        <v>-1.508</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3309</v>
+        <v>5.3095</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8649</v>
+        <v>2.8232</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.0127</v>
+        <v>-2.0242</v>
       </c>
       <c r="L2" t="n">
-        <v>4.8777</v>
+        <v>4.8474</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.9784</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5019</v>
+        <v>0.5162</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5051</v>
+        <v>-0.2415</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1875</v>
+        <v>-0.2349</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3176</v>
+        <v>-0.0066</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6621</v>
+        <v>4.1657</v>
       </c>
       <c r="E3" t="n">
-        <v>2.387</v>
+        <v>1.7843</v>
       </c>
       <c r="F3" t="n">
-        <v>2.275</v>
+        <v>2.3814</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1682</v>
+        <v>2.3411</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9234</v>
+        <v>0.0517</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2448</v>
+        <v>2.2894</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1457</v>
+        <v>1.8799</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2555</v>
+        <v>0.3685</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8902</v>
+        <v>1.5114</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0224</v>
+        <v>0.4613</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3546</v>
+        <v>0.778</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3332</v>
+        <v>0.2312</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8953</v>
+        <v>-0.0955</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4379</v>
+        <v>0.3267</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8598</v>
+        <v>3.8154</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7907</v>
+        <v>1.7641</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0691</v>
+        <v>2.0512</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3443</v>
+        <v>4.1629</v>
       </c>
       <c r="H4" t="n">
-        <v>0.052</v>
+        <v>2.9238</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2923</v>
+        <v>1.2391</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9087</v>
+        <v>4.1189</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3841</v>
+        <v>3.2405</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5246</v>
+        <v>0.8783</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4356</v>
+        <v>0.044</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7678</v>
+        <v>0.3608</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0723</v>
+        <v>0.4947</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1179</v>
+        <v>0.3085</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0457</v>
+        <v>0.1862</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4527</v>
+        <v>3.7565</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4326</v>
+        <v>0.485</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0202</v>
+        <v>3.2715</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3993</v>
+        <v>3.4104</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="I5" t="n">
         <v>3.6838</v>
       </c>
       <c r="J5" t="n">
-        <v>0.986</v>
+        <v>0.9686</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6132</v>
+        <v>-0.6173</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5992</v>
+        <v>1.5858</v>
       </c>
       <c r="M5" t="n">
-        <v>2.4133</v>
+        <v>2.4418</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3288</v>
+        <v>0.3438</v>
       </c>
       <c r="O5" t="n">
-        <v>2.0846</v>
+        <v>2.098</v>
       </c>
       <c r="P5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7613</v>
+        <v>-0.4749</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3266</v>
+        <v>-0.2559</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4346</v>
+        <v>-0.219</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3188</v>
+        <v>2.5184</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9792</v>
+        <v>0.9664</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3397</v>
+        <v>1.552</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2612</v>
+        <v>1.2761</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7574</v>
+        <v>0.7664</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5038</v>
+        <v>0.5097</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6365</v>
+        <v>0.628</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2639</v>
+        <v>-0.2683</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6247</v>
+        <v>0.6481</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6248</v>
+        <v>-0.4389</v>
       </c>
       <c r="T6" t="n">
-        <v>0.248</v>
+        <v>0.2505</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8729</v>
+        <v>-0.6895</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2767</v>
+        <v>1.9935</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7345</v>
+        <v>1.227</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5421</v>
+        <v>0.7665</v>
       </c>
       <c r="G7" t="n">
-        <v>4.9575</v>
+        <v>4.9616</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9667</v>
+        <v>1.9673</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9908</v>
+        <v>2.9943</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5892</v>
+        <v>3.566</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4648</v>
+        <v>1.4511</v>
       </c>
       <c r="L7" t="n">
-        <v>2.1243</v>
+        <v>2.1148</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3683</v>
+        <v>1.3956</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5019</v>
+        <v>0.5162</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2044</v>
+        <v>-0.4901</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7047</v>
+        <v>0.2364</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9092</v>
+        <v>-0.7265</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.2495</v>
+        <v>-2.2504</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8795</v>
+        <v>1.9281</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0857</v>
+        <v>0.6006</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7938</v>
+        <v>1.3276</v>
       </c>
       <c r="G8" t="n">
-        <v>5.7654</v>
+        <v>5.7776</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0922</v>
+        <v>2.0964</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6732</v>
+        <v>3.6812</v>
       </c>
       <c r="J8" t="n">
-        <v>4.008</v>
+        <v>3.9951</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7317</v>
+        <v>1.7237</v>
       </c>
       <c r="L8" t="n">
-        <v>2.2763</v>
+        <v>2.2714</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7574</v>
+        <v>1.7825</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3968</v>
+        <v>1.4097</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4095</v>
+        <v>-0.3714</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8166</v>
+        <v>-0.2744</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4071</v>
+        <v>-0.097</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.7959</v>
+        <v>-2.7951</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3676</v>
+        <v>1.7423</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4126</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7801</v>
+        <v>2.6763</v>
       </c>
       <c r="G9" t="n">
-        <v>2.434</v>
+        <v>2.4442</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.117</v>
+        <v>-0.1123</v>
       </c>
       <c r="I9" t="n">
-        <v>2.551</v>
+        <v>2.5564</v>
       </c>
       <c r="J9" t="n">
-        <v>1.258</v>
+        <v>1.2501</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9405</v>
+        <v>1.9363</v>
       </c>
       <c r="M9" t="n">
-        <v>1.176</v>
+        <v>1.1941</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5655</v>
+        <v>0.574</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.522</v>
+        <v>-0.1555</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7652</v>
+        <v>-0.272</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2431</v>
+        <v>0.1165</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3659</v>
+        <v>1.5419</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0538</v>
+        <v>1.286</v>
       </c>
       <c r="F10" t="n">
-        <v>0.312</v>
+        <v>0.2559</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1112</v>
+        <v>1.1123</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0952</v>
+        <v>1.0943</v>
       </c>
       <c r="I10" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2444</v>
+        <v>1.2397</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7966</v>
+        <v>0.7929</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4478</v>
+        <v>0.4468</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1331</v>
+        <v>-0.1275</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2986</v>
+        <v>0.3014</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.199</v>
+        <v>-0.0256</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1905</v>
+        <v>0.0463</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0726</v>
+        <v>0.5483</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9747</v>
+        <v>-1.8433</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0473</v>
+        <v>2.3916</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0959</v>
+        <v>1.0767</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.8134</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2718</v>
+        <v>0.2633</v>
       </c>
       <c r="J11" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0258</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9831</v>
+        <v>0.9578</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.9091</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>1.022</v>
+        <v>1.0509</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1809</v>
+        <v>1.1953</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8892</v>
+        <v>-0.3902</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0998</v>
+        <v>0.0902</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7894</v>
+        <v>-0.4804</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2439</v>
+        <v>-0.2936</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2061</v>
+        <v>-1.8115</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9622</v>
+        <v>1.518</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2061</v>
+        <v>-0.2089</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7764</v>
+        <v>-0.7701</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5703</v>
+        <v>0.5612</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4433</v>
+        <v>0.4209</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1456</v>
+        <v>-0.1519</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5889</v>
+        <v>0.5728</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6494</v>
+        <v>-0.6298</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4158</v>
+        <v>0.3706</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3811</v>
+        <v>0.0439</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.3267</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3719</v>
+        <v>-1.634</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1766</v>
+        <v>-2.3704</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8047</v>
+        <v>0.7365</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5631</v>
+        <v>-0.5542</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0247</v>
+        <v>-0.0149</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5384</v>
+        <v>-0.5393</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5905</v>
+        <v>-0.5994</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6771</v>
+        <v>-0.6856</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0274</v>
+        <v>0.0452</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7752</v>
+        <v>0.5168</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0393</v>
+        <v>-0.1258</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7358</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4498</v>
+        <v>-0.4584</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6429</v>
+        <v>0.6311</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>24.9549</v>
+        <v>25.6425</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4221</v>
+        <v>4.783199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>20.5326</v>
+        <v>20.8595</v>
       </c>
       <c r="G14" t="n">
-        <v>29.5879</v>
+        <v>29.6013</v>
       </c>
       <c r="H14" t="n">
-        <v>6.9977</v>
+        <v>7.034599999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>22.5903</v>
+        <v>22.5666</v>
       </c>
       <c r="J14" t="n">
-        <v>20.5681</v>
+        <v>20.3168</v>
       </c>
       <c r="K14" t="n">
-        <v>6.1489</v>
+        <v>6.037399999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>14.4194</v>
+        <v>14.2791</v>
       </c>
       <c r="M14" t="n">
-        <v>9.0197</v>
+        <v>9.284600000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8487999999999998</v>
+        <v>0.9970000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>8.170900000000001</v>
+        <v>8.2874</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2682</v>
+        <v>2.2762</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.0125</v>
+        <v>-17.0722</v>
       </c>
       <c r="R14" t="n">
-        <v>19.2809</v>
+        <v>19.3489</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6634</v>
+        <v>-0.9748</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9978999999999999</v>
+        <v>-0.2827000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6657</v>
+        <v>-0.6922</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.2379</v>
+        <v>-5.2598</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8644</v>
+        <v>1.8217</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.1023</v>
+        <v>-7.0815</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.4047</v>
+        <v>4.4244</v>
       </c>
       <c r="E15" t="n">
-        <v>6.8618</v>
+        <v>4.9335</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4571</v>
+        <v>-0.5092</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7094</v>
+        <v>2.7028</v>
       </c>
       <c r="H15" t="n">
-        <v>2.107</v>
+        <v>2.0917</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6025</v>
+        <v>0.6111</v>
       </c>
       <c r="J15" t="n">
-        <v>5.2701</v>
+        <v>5.2337</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5487</v>
+        <v>2.5231</v>
       </c>
       <c r="L15" t="n">
-        <v>2.7214</v>
+        <v>2.7106</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5606</v>
+        <v>-2.5309</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.1189</v>
+        <v>-2.0995</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1509</v>
+        <v>1.1752</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7674</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3835</v>
+        <v>0.2886</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.431</v>
+        <v>0.9637</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1867</v>
+        <v>1.2233</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7557</v>
+        <v>-0.2596</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3422</v>
+        <v>0.3455</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7793</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4371</v>
+        <v>-0.4302</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4902</v>
+        <v>1.4767</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3782</v>
+        <v>1.365</v>
       </c>
       <c r="L16" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.148</v>
+        <v>-1.1312</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3176</v>
+        <v>-0.1557</v>
       </c>
       <c r="T16" t="n">
-        <v>0.738</v>
+        <v>-0.2047</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4204</v>
+        <v>0.049</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7326</v>
+        <v>0.8033</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7335</v>
+        <v>-0.2732</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4661</v>
+        <v>1.0765</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5809</v>
+        <v>-0.5799</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3117</v>
+        <v>-0.3103</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2692</v>
+        <v>-0.2696</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0379</v>
+        <v>-0.0499</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1141</v>
+        <v>0.1067</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5431</v>
+        <v>-0.53</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0475</v>
+        <v>0.0174</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6956</v>
+        <v>-0.2232</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6481</v>
+        <v>0.2407</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2773</v>
+        <v>-0.7603</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6398</v>
+        <v>-1.3134</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3625</v>
+        <v>0.5531</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0753</v>
+        <v>-2.0778</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3983</v>
+        <v>0.3964</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.4736</v>
+        <v>-2.4743</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.666</v>
+        <v>-0.6929</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6509</v>
+        <v>0.641</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3169</v>
+        <v>-1.334</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4094</v>
+        <v>-1.3849</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1567</v>
+        <v>-1.1403</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.0498</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9739</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4128</v>
+        <v>0.5707</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5879</v>
+        <v>-1.2467</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7757</v>
+        <v>-1.667</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1879</v>
+        <v>0.4203</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8659</v>
+        <v>-0.8605</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0289</v>
+        <v>-0.0233</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.837</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1547</v>
+        <v>-0.1594</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1893</v>
+        <v>-0.1939</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7113</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8127</v>
+        <v>-0.4773</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4869</v>
+        <v>-0.3695</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3257</v>
+        <v>-0.1078</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1414</v>
+        <v>-1.9787</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6335</v>
+        <v>-2.0725</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.508</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.5201</v>
+        <v>-4.5146</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.1874</v>
+        <v>-3.1907</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3327</v>
+        <v>-1.3239</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.474</v>
+        <v>-2.4996</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.7298</v>
+        <v>-2.7449</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0461</v>
+        <v>-2.015</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5885</v>
+        <v>-1.5692</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1245</v>
+        <v>0.0302</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0253</v>
+        <v>-0.4348</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0992</v>
+        <v>0.465</v>
       </c>
       <c r="V20" t="n">
-        <v>1.369</v>
+        <v>1.3675</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2763</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2502</v>
+        <v>-3.3003</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5519</v>
+        <v>-3.585</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3017</v>
+        <v>0.2847</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.614</v>
+        <v>-4.6113</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1889</v>
+        <v>-1.1945</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.4251</v>
+        <v>-3.4168</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.1143</v>
+        <v>-3.141</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9045</v>
+        <v>-0.921</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.2098</v>
+        <v>-2.22</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4998</v>
+        <v>-1.4703</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2153</v>
+        <v>-1.1968</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8626</v>
+        <v>0.8038</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1693</v>
+        <v>-0.1677</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0319</v>
+        <v>0.9715</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5012</v>
+        <v>0.5072</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5914</v>
+        <v>-0.5822000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4235</v>
+        <v>-3.3702</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5917</v>
+        <v>-3.1619</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8318</v>
+        <v>-0.2083</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.856</v>
+        <v>-3.8661</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7876</v>
+        <v>-1.8001</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0684</v>
+        <v>-2.066</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3163</v>
+        <v>-2.3509</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1886</v>
+        <v>-1.2108</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1276</v>
+        <v>-1.1401</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5398</v>
+        <v>-1.5152</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9408</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7528</v>
+        <v>0.317</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0998</v>
+        <v>0.3758</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.653</v>
+        <v>-0.0589</v>
       </c>
       <c r="V22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3163</v>
+        <v>-4.8428</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.8207</v>
+        <v>-3.8002</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4956</v>
+        <v>-1.0426</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.4893</v>
+        <v>-4.8034</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4979</v>
+        <v>-2.252</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.9873</v>
+        <v>-2.5514</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7851</v>
+        <v>-1.8091</v>
       </c>
       <c r="K23" t="n">
-        <v>1.475</v>
+        <v>-1.1311</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.2601</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.7043</v>
+        <v>-2.9943</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9771</v>
+        <v>-1.1209</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7272</v>
+        <v>-1.8734</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.4952</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.7635</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0062</v>
+        <v>0.2971</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6352</v>
+        <v>0.5128</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3711</v>
+        <v>-0.2157</v>
       </c>
       <c r="V23" t="n">
-        <v>0.662</v>
+        <v>-0.1089</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.4307</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6345</v>
+        <v>-5.5502</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3737</v>
+        <v>-4.8738</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2608</v>
+        <v>-0.6764</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.8157</v>
+        <v>-4.502</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.2569</v>
+        <v>0.4915</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.5588</v>
+        <v>-4.9935</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.7969</v>
+        <v>-1.8235</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1225</v>
+        <v>1.4544</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6744</v>
+        <v>-3.2779</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.0188</v>
+        <v>-2.6784</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1344</v>
+        <v>-0.9629</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.8844</v>
+        <v>-1.7155</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.4952</v>
+        <v>-4.7803</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4827</v>
+        <v>0.7907</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.6405</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4011</v>
+        <v>0.1503</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1093</v>
+        <v>0.665</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1093</v>
+        <v>-0.4245</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.891999999999999</v>
+        <v>-8.508599999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.4605</v>
+        <v>-6.2691</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4315</v>
+        <v>-2.2395</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.8221</v>
+        <v>-6.834</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.0187</v>
+        <v>-2.0191</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.8034</v>
+        <v>-4.815</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.435</v>
+        <v>-3.4686</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.1052</v>
+        <v>-1.1139</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.3299</v>
+        <v>-2.3547</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.387</v>
+        <v>-3.3654</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.4735</v>
+        <v>-2.4603</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1074</v>
+        <v>0.5027</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0575</v>
+        <v>0.2968</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0499</v>
+        <v>0.2058</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.8163</v>
+        <v>-0.8114</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.3627</v>
+        <v>-1.3562</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-24.9548</v>
+        <v>-23.3664</v>
       </c>
       <c r="E26" t="n">
-        <v>-20.5325</v>
+        <v>-20.8593</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.4223</v>
+        <v>-2.5072</v>
       </c>
       <c r="G26" t="n">
-        <v>-29.5877</v>
+        <v>-29.6013</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.997599999999999</v>
+        <v>-7.0347</v>
       </c>
       <c r="I26" t="n">
-        <v>-22.5901</v>
+        <v>-22.5668</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.0199</v>
+        <v>-9.2845</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.8490999999999991</v>
+        <v>-0.9970000000000003</v>
       </c>
       <c r="L26" t="n">
-        <v>-8.1708</v>
+        <v>-8.2875</v>
       </c>
       <c r="M26" t="n">
-        <v>-20.5682</v>
+        <v>-20.3167</v>
       </c>
       <c r="N26" t="n">
-        <v>-6.1487</v>
+        <v>-6.0375</v>
       </c>
       <c r="O26" t="n">
-        <v>-14.4192</v>
+        <v>-14.2791</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.2682</v>
+        <v>-2.2761</v>
       </c>
       <c r="Q26" t="n">
-        <v>-19.2808</v>
+        <v>-19.3487</v>
       </c>
       <c r="R26" t="n">
-        <v>17.0125</v>
+        <v>17.0725</v>
       </c>
       <c r="S26" t="n">
-        <v>1.6635</v>
+        <v>3.2513</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6657</v>
+        <v>0.6920999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>0.9979</v>
+        <v>2.5592</v>
       </c>
       <c r="V26" t="n">
-        <v>5.2378</v>
+        <v>5.2598</v>
       </c>
       <c r="W26" t="n">
-        <v>7.102499999999999</v>
+        <v>7.0817</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.8645</v>
+        <v>-1.8217</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104528_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104528_W8.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.0815</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.278</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.5822000000000001</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.4245</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.3562</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104528_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-1.8217</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
